--- a/public/PresupuestoInicial/presupuesto egresos capitulo 7000.xlsx
+++ b/public/PresupuestoInicial/presupuesto egresos capitulo 7000.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11210"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27928"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/gustavor/Documents/Github/SAC-IPE/public/PresupuestoInicial/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\RMartinez\Desktop\CargaPres\PresupuestoInicial\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A24D5289-8214-3341-A382-79DCCBB78E1E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{74B13F1B-270E-4477-B4F8-9FF9C6C93D3E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="760" windowWidth="30240" windowHeight="17640" xr2:uid="{D5EA5309-C82F-4CC7-B652-D8F0609F03B5}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{D5EA5309-C82F-4CC7-B652-D8F0609F03B5}"/>
   </bookViews>
   <sheets>
     <sheet name="Formato de Carga 7" sheetId="5" r:id="rId1"/>
@@ -142,7 +142,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -275,9 +275,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Tema de Office">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - Tema de 2022">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -315,7 +315,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -421,7 +421,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -563,7 +563,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -572,24 +572,24 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B450B356-E8E6-4902-AA25-5288A335BBFE}">
   <dimension ref="A1:W23"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="5.5" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="6.6640625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="17.33203125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="5.5" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="3.5" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="4.83203125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="16.5" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="91.33203125" customWidth="1"/>
-    <col min="10" max="10" width="27.5" customWidth="1"/>
-    <col min="11" max="11" width="16.33203125" style="10" bestFit="1" customWidth="1"/>
-    <col min="12" max="22" width="14.6640625" style="10" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="16.5" style="10" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="5.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="6.7109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="17.28515625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="5.42578125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="3.42578125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="4.85546875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="16.42578125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="91.28515625" customWidth="1"/>
+    <col min="10" max="10" width="27.42578125" customWidth="1"/>
+    <col min="11" max="11" width="16.28515625" style="10" bestFit="1" customWidth="1"/>
+    <col min="12" max="22" width="14.7109375" style="10" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="16.42578125" style="10" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:23" ht="35" thickBot="1">
+    <row r="1" spans="1:23" ht="48" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="5" t="s">
         <v>12</v>
       </c>
@@ -660,7 +660,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="2" spans="1:23" s="3" customFormat="1" ht="16">
+    <row r="2" spans="1:23" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
         <v>31</v>
       </c>
@@ -732,7 +732,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:23" s="3" customFormat="1" ht="16">
+    <row r="3" spans="1:23" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="4" t="s">
         <v>31</v>
       </c>
@@ -804,7 +804,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:23" s="2" customFormat="1">
+    <row r="4" spans="1:23" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4"/>
       <c r="B4"/>
       <c r="C4"/>
@@ -829,7 +829,7 @@
       <c r="V4" s="11"/>
       <c r="W4" s="11"/>
     </row>
-    <row r="5" spans="1:23" s="2" customFormat="1">
+    <row r="5" spans="1:23" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5"/>
       <c r="B5"/>
       <c r="C5"/>
@@ -854,7 +854,7 @@
       <c r="V5" s="10"/>
       <c r="W5" s="10"/>
     </row>
-    <row r="6" spans="1:23" s="2" customFormat="1">
+    <row r="6" spans="1:23" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6"/>
       <c r="B6"/>
       <c r="C6"/>
@@ -879,7 +879,7 @@
       <c r="V6" s="10"/>
       <c r="W6" s="10"/>
     </row>
-    <row r="7" spans="1:23" s="2" customFormat="1">
+    <row r="7" spans="1:23" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7"/>
       <c r="B7"/>
       <c r="C7"/>
@@ -904,7 +904,7 @@
       <c r="V7" s="10"/>
       <c r="W7" s="10"/>
     </row>
-    <row r="8" spans="1:23" s="2" customFormat="1">
+    <row r="8" spans="1:23" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8"/>
       <c r="B8"/>
       <c r="C8"/>
@@ -929,7 +929,7 @@
       <c r="V8" s="10"/>
       <c r="W8" s="10"/>
     </row>
-    <row r="9" spans="1:23" s="2" customFormat="1">
+    <row r="9" spans="1:23" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9"/>
       <c r="B9"/>
       <c r="C9"/>
@@ -954,7 +954,7 @@
       <c r="V9" s="10"/>
       <c r="W9" s="10"/>
     </row>
-    <row r="10" spans="1:23" s="2" customFormat="1">
+    <row r="10" spans="1:23" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A10"/>
       <c r="B10"/>
       <c r="C10"/>
@@ -979,7 +979,7 @@
       <c r="V10" s="10"/>
       <c r="W10" s="10"/>
     </row>
-    <row r="11" spans="1:23" s="2" customFormat="1">
+    <row r="11" spans="1:23" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A11"/>
       <c r="B11"/>
       <c r="C11"/>
@@ -1004,7 +1004,7 @@
       <c r="V11" s="10"/>
       <c r="W11" s="10"/>
     </row>
-    <row r="12" spans="1:23" s="2" customFormat="1">
+    <row r="12" spans="1:23" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A12"/>
       <c r="B12"/>
       <c r="C12"/>
@@ -1029,7 +1029,7 @@
       <c r="V12" s="10"/>
       <c r="W12" s="10"/>
     </row>
-    <row r="13" spans="1:23" s="2" customFormat="1">
+    <row r="13" spans="1:23" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A13"/>
       <c r="B13"/>
       <c r="C13"/>
@@ -1054,7 +1054,7 @@
       <c r="V13" s="10"/>
       <c r="W13" s="10"/>
     </row>
-    <row r="14" spans="1:23" s="2" customFormat="1">
+    <row r="14" spans="1:23" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A14"/>
       <c r="B14"/>
       <c r="C14"/>
@@ -1079,7 +1079,7 @@
       <c r="V14" s="10"/>
       <c r="W14" s="10"/>
     </row>
-    <row r="15" spans="1:23" s="2" customFormat="1">
+    <row r="15" spans="1:23" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A15"/>
       <c r="B15"/>
       <c r="C15"/>
@@ -1104,7 +1104,7 @@
       <c r="V15" s="10"/>
       <c r="W15" s="10"/>
     </row>
-    <row r="16" spans="1:23" s="2" customFormat="1">
+    <row r="16" spans="1:23" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A16"/>
       <c r="B16"/>
       <c r="C16"/>
@@ -1129,7 +1129,7 @@
       <c r="V16" s="10"/>
       <c r="W16" s="10"/>
     </row>
-    <row r="17" spans="1:23" s="2" customFormat="1">
+    <row r="17" spans="1:23" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A17"/>
       <c r="B17"/>
       <c r="C17"/>
@@ -1154,7 +1154,7 @@
       <c r="V17" s="10"/>
       <c r="W17" s="10"/>
     </row>
-    <row r="18" spans="1:23" s="2" customFormat="1">
+    <row r="18" spans="1:23" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A18"/>
       <c r="B18"/>
       <c r="C18"/>
@@ -1179,7 +1179,7 @@
       <c r="V18" s="10"/>
       <c r="W18" s="10"/>
     </row>
-    <row r="19" spans="1:23" s="2" customFormat="1">
+    <row r="19" spans="1:23" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A19"/>
       <c r="B19"/>
       <c r="C19"/>
@@ -1204,7 +1204,7 @@
       <c r="V19" s="10"/>
       <c r="W19" s="10"/>
     </row>
-    <row r="20" spans="1:23" s="2" customFormat="1">
+    <row r="20" spans="1:23" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A20"/>
       <c r="B20"/>
       <c r="C20"/>
@@ -1229,7 +1229,7 @@
       <c r="V20" s="10"/>
       <c r="W20" s="10"/>
     </row>
-    <row r="21" spans="1:23" s="2" customFormat="1">
+    <row r="21" spans="1:23" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A21"/>
       <c r="B21"/>
       <c r="C21"/>
@@ -1254,7 +1254,7 @@
       <c r="V21" s="10"/>
       <c r="W21" s="10"/>
     </row>
-    <row r="22" spans="1:23" s="2" customFormat="1">
+    <row r="22" spans="1:23" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A22"/>
       <c r="B22"/>
       <c r="C22"/>
@@ -1279,7 +1279,7 @@
       <c r="V22" s="10"/>
       <c r="W22" s="10"/>
     </row>
-    <row r="23" spans="1:23" s="2" customFormat="1">
+    <row r="23" spans="1:23" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A23"/>
       <c r="B23"/>
       <c r="C23"/>
